--- a/FM-MN-07_CUTTING-01.xlsx
+++ b/FM-MN-07_CUTTING-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56052BC-2860-4629-AA4D-FBF3D9FFD0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A5A832-6104-4F64-A969-E5410EF5FF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>ใบตรวจสอบเครื่อง CUTTING</t>
   </si>
@@ -40,9 +40,6 @@
     <t xml:space="preserve">การ Worm spindle ก่อนเริ่มงาน เพื่อตรวจ ความผิดปกติของชุด Back gauge และ Motor </t>
   </si>
   <si>
-    <t>/</t>
-  </si>
-  <si>
     <t>เช็ค Auto Up-Down back gauge และ Manual ( ความคล่องตัวในการเคลื่อนที่ )</t>
   </si>
   <si>
@@ -50,9 +47,6 @@
   </si>
   <si>
     <t>ตรวจเช็ค  Switch  เปิด-ปิด</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>ตรวจสอบ Digital  read out และการทำงานของ Linear  scale</t>
@@ -67,20 +61,7 @@
     <t xml:space="preserve">ตรวจสอบความพร้อมสภาพโดยรวมของเครื่อง จักรและอุปกรณ์เสริมต่าง ๆ </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>นาย C</t>
-  </si>
-  <si>
-    <t>พลวัฒน์</t>
-  </si>
-  <si>
     <t>บันทึกเพิ่มเติม</t>
-  </si>
-  <si>
-    <t>📌 [วันที่ 25/05/2026]
-ข้อ 4: switch เสีย</t>
   </si>
   <si>
     <t>ผู้จัดการแผนกซ่อมบำรุง</t>
@@ -422,12 +403,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -435,34 +417,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -490,13 +471,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2286000</xdr:colOff>
+      <xdr:colOff>2343150</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4324350</xdr:colOff>
+      <xdr:colOff>4381500</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>160866</xdr:rowOff>
     </xdr:to>
@@ -522,7 +503,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2600325" y="3895725"/>
+          <a:off x="2657475" y="2895600"/>
           <a:ext cx="2038350" cy="970491"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1520,80 +1501,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
     </row>
     <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="21" t="s">
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
     </row>
     <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="16"/>
@@ -1631,49 +1612,49 @@
       <c r="AG3" s="14"/>
     </row>
     <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="34"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="29"/>
     </row>
     <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="24"/>
-      <c r="B5" s="37"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="11">
         <v>1</v>
       </c>
@@ -1799,9 +1780,7 @@
       <c r="X6" s="20"/>
       <c r="Y6" s="20"/>
       <c r="Z6" s="20"/>
-      <c r="AA6" s="20" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20"/>
       <c r="AD6" s="20"/>
@@ -1814,7 +1793,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -1840,9 +1819,7 @@
       <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
-      <c r="AA7" s="20" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20"/>
       <c r="AD7" s="20"/>
@@ -1855,7 +1832,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
@@ -1881,9 +1858,7 @@
       <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
-      <c r="AA8" s="20" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20"/>
       <c r="AD8" s="20"/>
@@ -1896,7 +1871,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -1922,9 +1897,7 @@
       <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
-      <c r="AA9" s="20" t="s">
-        <v>10</v>
-      </c>
+      <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20"/>
       <c r="AD9" s="20"/>
@@ -1937,7 +1910,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -1963,9 +1936,7 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
-      <c r="AA10" s="20" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20"/>
       <c r="AD10" s="20"/>
@@ -1978,7 +1949,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -2004,9 +1975,7 @@
       <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="20" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20"/>
       <c r="AD11" s="20"/>
@@ -2019,7 +1988,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -2045,9 +2014,7 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="20"/>
-      <c r="AA12" s="20" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20"/>
       <c r="AD12" s="20"/>
@@ -2060,7 +2027,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -2086,9 +2053,7 @@
       <c r="X13" s="20"/>
       <c r="Y13" s="20"/>
       <c r="Z13" s="20"/>
-      <c r="AA13" s="20" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20"/>
       <c r="AD13" s="20"/>
@@ -2099,154 +2064,148 @@
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="6"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="6"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB16" s="25"/>
-      <c r="AC16" s="25"/>
-      <c r="AD16" s="25"/>
-      <c r="AE16" s="25"/>
-      <c r="AF16" s="25"/>
-      <c r="AG16" s="25"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="37"/>
+      <c r="AB16" s="26"/>
+      <c r="AC16" s="26"/>
+      <c r="AD16" s="26"/>
+      <c r="AE16" s="26"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="6"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
     </row>
     <row r="18" spans="2:33" ht="12" customHeight="1"/>
     <row r="19" spans="2:33" ht="19.5" customHeight="1">
       <c r="B19" s="17" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:33" ht="195" customHeight="1">
-      <c r="B20" s="38" t="s">
-        <v>19</v>
-      </c>
+    <row r="20" spans="2:33" ht="275.25" customHeight="1">
+      <c r="B20" s="21"/>
     </row>
     <row r="21" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="22" spans="2:33" ht="21" customHeight="1">
@@ -2259,13 +2218,13 @@
       <c r="AG22" s="32"/>
     </row>
     <row r="23" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC23" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="28"/>
-      <c r="AG23" s="28"/>
+      <c r="AC23" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD23" s="34"/>
+      <c r="AE23" s="34"/>
+      <c r="AF23" s="34"/>
+      <c r="AG23" s="34"/>
     </row>
     <row r="24" spans="2:33" ht="7.5" customHeight="1">
       <c r="D24" s="4"/>
@@ -2273,11 +2232,65 @@
     <row r="25" spans="2:33" ht="14.25" customHeight="1">
       <c r="C25" s="3"/>
       <c r="AG25" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="AC23:AG23"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="V16:V17"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="AG14:AG15"/>
     <mergeCell ref="AB14:AB15"/>
@@ -2294,64 +2307,10 @@
     <mergeCell ref="AA14:AA15"/>
     <mergeCell ref="P14:P15"/>
     <mergeCell ref="J14:J15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="AC22:AG22"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="AC23:AG23"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="U16:U17"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="AE16:AE17"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="AG16:AG17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="78" orientation="landscape" horizontalDpi="4294967292"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="78" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/FM-MN-07_CUTTING-01.xlsx
+++ b/FM-MN-07_CUTTING-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A5A832-6104-4F64-A969-E5410EF5FF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75094396-E1C8-40EE-AF7E-D7F0BB77C9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,13 +403,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -417,33 +416,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1501,80 +1501,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="38" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
     </row>
     <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="38" t="s">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
     </row>
     <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="16"/>
@@ -1612,49 +1612,49 @@
       <c r="AG3" s="14"/>
     </row>
     <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="29"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="36"/>
     </row>
     <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="23"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="11">
         <v>1</v>
       </c>
@@ -2064,139 +2064,139 @@
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="37"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="6"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="25"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="24"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="24"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="24"/>
+      <c r="AE15" s="24"/>
+      <c r="AF15" s="24"/>
+      <c r="AG15" s="24"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="6"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="26"/>
-      <c r="W16" s="26"/>
-      <c r="X16" s="26"/>
-      <c r="Y16" s="26"/>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="37"/>
-      <c r="AB16" s="26"/>
-      <c r="AC16" s="26"/>
-      <c r="AD16" s="26"/>
-      <c r="AE16" s="26"/>
-      <c r="AF16" s="26"/>
-      <c r="AG16" s="26"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="6"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="25"/>
-      <c r="AD17" s="25"/>
-      <c r="AE17" s="25"/>
-      <c r="AF17" s="25"/>
-      <c r="AG17" s="25"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
     </row>
     <row r="18" spans="2:33" ht="12" customHeight="1"/>
     <row r="19" spans="2:33" ht="19.5" customHeight="1">
@@ -2205,7 +2205,38 @@
       </c>
     </row>
     <row r="20" spans="2:33" ht="275.25" customHeight="1">
-      <c r="B20" s="21"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="38"/>
+      <c r="AE20" s="38"/>
+      <c r="AF20" s="38"/>
+      <c r="AG20" s="38"/>
     </row>
     <row r="21" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="22" spans="2:33" ht="21" customHeight="1">
@@ -2218,13 +2249,13 @@
       <c r="AG22" s="32"/>
     </row>
     <row r="23" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC23" s="33" t="s">
+      <c r="AC23" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="AD23" s="34"/>
-      <c r="AE23" s="34"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="34"/>
+      <c r="AD23" s="28"/>
+      <c r="AE23" s="28"/>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="28"/>
     </row>
     <row r="24" spans="2:33" ht="7.5" customHeight="1">
       <c r="D24" s="4"/>
@@ -2236,40 +2267,24 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="AE16:AE17"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="AG16:AG17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="U16:U17"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="T16:T17"/>
+  <mergeCells count="71">
+    <mergeCell ref="B20:AG20"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="J14:J15"/>
     <mergeCell ref="AC23:AG23"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="A1:AA2"/>
@@ -2286,27 +2301,44 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="R14:R15"/>
     <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="T16:T17"/>
     <mergeCell ref="Q16:Q17"/>
     <mergeCell ref="O14:O15"/>
     <mergeCell ref="S16:S17"/>
     <mergeCell ref="X14:X15"/>
     <mergeCell ref="V16:V17"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="AG14:AG15"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AG16:AG17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_CUTTING-01.xlsx
+++ b/FM-MN-07_CUTTING-01.xlsx
@@ -1726,41 +1726,37 @@
           <t xml:space="preserve">การ Worm spindle ก่อนเริ่มงาน เพื่อตรวจ ความผิดปกติของชุด Back gauge และ Motor </t>
         </is>
       </c>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="20" t="n"/>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="20" t="n"/>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="20" t="n"/>
-      <c r="O6" s="20" t="n"/>
-      <c r="P6" s="20" t="n"/>
-      <c r="Q6" s="20" t="n"/>
-      <c r="R6" s="20" t="n"/>
-      <c r="S6" s="20" t="n"/>
-      <c r="T6" s="20" t="n"/>
-      <c r="U6" s="20" t="n"/>
-      <c r="V6" s="20" t="n"/>
-      <c r="W6" s="20" t="n"/>
-      <c r="X6" s="20" t="n"/>
-      <c r="Y6" s="20" t="n"/>
-      <c r="Z6" s="20" t="n"/>
-      <c r="AA6" s="20" t="n"/>
-      <c r="AB6" s="20" t="n"/>
-      <c r="AC6" s="20" t="n"/>
-      <c r="AD6" s="20" t="n"/>
-      <c r="AE6" s="20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF6" s="20" t="n"/>
-      <c r="AG6" s="20" t="n"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="20" t="inlineStr"/>
+      <c r="W6" s="20" t="inlineStr"/>
+      <c r="X6" s="20" t="inlineStr"/>
+      <c r="Y6" s="20" t="inlineStr"/>
+      <c r="Z6" s="20" t="inlineStr"/>
+      <c r="AA6" s="20" t="inlineStr"/>
+      <c r="AB6" s="20" t="inlineStr"/>
+      <c r="AC6" s="20" t="inlineStr"/>
+      <c r="AD6" s="20" t="inlineStr"/>
+      <c r="AE6" s="20" t="inlineStr"/>
+      <c r="AF6" s="20" t="inlineStr"/>
+      <c r="AG6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A7" s="9" t="n">
@@ -1771,41 +1767,37 @@
           <t>เช็ค Auto Up-Down back gauge และ Manual ( ความคล่องตัวในการเคลื่อนที่ )</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="20" t="n"/>
-      <c r="P7" s="20" t="n"/>
-      <c r="Q7" s="20" t="n"/>
-      <c r="R7" s="20" t="n"/>
-      <c r="S7" s="20" t="n"/>
-      <c r="T7" s="20" t="n"/>
-      <c r="U7" s="20" t="n"/>
-      <c r="V7" s="20" t="n"/>
-      <c r="W7" s="20" t="n"/>
-      <c r="X7" s="20" t="n"/>
-      <c r="Y7" s="20" t="n"/>
-      <c r="Z7" s="20" t="n"/>
-      <c r="AA7" s="20" t="n"/>
-      <c r="AB7" s="20" t="n"/>
-      <c r="AC7" s="20" t="n"/>
-      <c r="AD7" s="20" t="n"/>
-      <c r="AE7" s="20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF7" s="20" t="n"/>
-      <c r="AG7" s="20" t="n"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="20" t="inlineStr"/>
+      <c r="W7" s="20" t="inlineStr"/>
+      <c r="X7" s="20" t="inlineStr"/>
+      <c r="Y7" s="20" t="inlineStr"/>
+      <c r="Z7" s="20" t="inlineStr"/>
+      <c r="AA7" s="20" t="inlineStr"/>
+      <c r="AB7" s="20" t="inlineStr"/>
+      <c r="AC7" s="20" t="inlineStr"/>
+      <c r="AD7" s="20" t="inlineStr"/>
+      <c r="AE7" s="20" t="inlineStr"/>
+      <c r="AF7" s="20" t="inlineStr"/>
+      <c r="AG7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A8" s="9" t="n">
@@ -1816,41 +1808,37 @@
           <t>ระดับน้ำมันไฮดรอลิค ตรวจสอบระดับในปั้มน้ำมัน หล่อลืนแกน  Back gauge</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="20" t="n"/>
-      <c r="P8" s="20" t="n"/>
-      <c r="Q8" s="20" t="n"/>
-      <c r="R8" s="20" t="n"/>
-      <c r="S8" s="20" t="n"/>
-      <c r="T8" s="20" t="n"/>
-      <c r="U8" s="20" t="n"/>
-      <c r="V8" s="20" t="n"/>
-      <c r="W8" s="20" t="n"/>
-      <c r="X8" s="20" t="n"/>
-      <c r="Y8" s="20" t="n"/>
-      <c r="Z8" s="20" t="n"/>
-      <c r="AA8" s="20" t="n"/>
-      <c r="AB8" s="20" t="n"/>
-      <c r="AC8" s="20" t="n"/>
-      <c r="AD8" s="20" t="n"/>
-      <c r="AE8" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="20" t="n"/>
-      <c r="AG8" s="20" t="n"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
+      <c r="K8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="inlineStr"/>
+      <c r="O8" s="20" t="inlineStr"/>
+      <c r="P8" s="20" t="inlineStr"/>
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="20" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="20" t="inlineStr"/>
+      <c r="W8" s="20" t="inlineStr"/>
+      <c r="X8" s="20" t="inlineStr"/>
+      <c r="Y8" s="20" t="inlineStr"/>
+      <c r="Z8" s="20" t="inlineStr"/>
+      <c r="AA8" s="20" t="inlineStr"/>
+      <c r="AB8" s="20" t="inlineStr"/>
+      <c r="AC8" s="20" t="inlineStr"/>
+      <c r="AD8" s="20" t="inlineStr"/>
+      <c r="AE8" s="20" t="inlineStr"/>
+      <c r="AF8" s="20" t="inlineStr"/>
+      <c r="AG8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A9" s="9" t="n">
@@ -1861,41 +1849,37 @@
           <t>ตรวจเช็ค  Switch  เปิด-ปิด</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="20" t="n"/>
-      <c r="P9" s="20" t="n"/>
-      <c r="Q9" s="20" t="n"/>
-      <c r="R9" s="20" t="n"/>
-      <c r="S9" s="20" t="n"/>
-      <c r="T9" s="20" t="n"/>
-      <c r="U9" s="20" t="n"/>
-      <c r="V9" s="20" t="n"/>
-      <c r="W9" s="20" t="n"/>
-      <c r="X9" s="20" t="n"/>
-      <c r="Y9" s="20" t="n"/>
-      <c r="Z9" s="20" t="n"/>
-      <c r="AA9" s="20" t="n"/>
-      <c r="AB9" s="20" t="n"/>
-      <c r="AC9" s="20" t="n"/>
-      <c r="AD9" s="20" t="n"/>
-      <c r="AE9" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="20" t="n"/>
-      <c r="AG9" s="20" t="n"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="20" t="inlineStr"/>
+      <c r="W9" s="20" t="inlineStr"/>
+      <c r="X9" s="20" t="inlineStr"/>
+      <c r="Y9" s="20" t="inlineStr"/>
+      <c r="Z9" s="20" t="inlineStr"/>
+      <c r="AA9" s="20" t="inlineStr"/>
+      <c r="AB9" s="20" t="inlineStr"/>
+      <c r="AC9" s="20" t="inlineStr"/>
+      <c r="AD9" s="20" t="inlineStr"/>
+      <c r="AE9" s="20" t="inlineStr"/>
+      <c r="AF9" s="20" t="inlineStr"/>
+      <c r="AG9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A10" s="9" t="n">
@@ -1906,41 +1890,37 @@
           <t>ตรวจสอบ Digital  read out และการทำงานของ Linear  scale</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="20" t="n"/>
-      <c r="P10" s="20" t="n"/>
-      <c r="Q10" s="20" t="n"/>
-      <c r="R10" s="20" t="n"/>
-      <c r="S10" s="20" t="n"/>
-      <c r="T10" s="20" t="n"/>
-      <c r="U10" s="20" t="n"/>
-      <c r="V10" s="20" t="n"/>
-      <c r="W10" s="20" t="n"/>
-      <c r="X10" s="20" t="n"/>
-      <c r="Y10" s="20" t="n"/>
-      <c r="Z10" s="20" t="n"/>
-      <c r="AA10" s="20" t="n"/>
-      <c r="AB10" s="20" t="n"/>
-      <c r="AC10" s="20" t="n"/>
-      <c r="AD10" s="20" t="n"/>
-      <c r="AE10" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="20" t="n"/>
-      <c r="AG10" s="20" t="n"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="20" t="inlineStr"/>
+      <c r="W10" s="20" t="inlineStr"/>
+      <c r="X10" s="20" t="inlineStr"/>
+      <c r="Y10" s="20" t="inlineStr"/>
+      <c r="Z10" s="20" t="inlineStr"/>
+      <c r="AA10" s="20" t="inlineStr"/>
+      <c r="AB10" s="20" t="inlineStr"/>
+      <c r="AC10" s="20" t="inlineStr"/>
+      <c r="AD10" s="20" t="inlineStr"/>
+      <c r="AE10" s="20" t="inlineStr"/>
+      <c r="AF10" s="20" t="inlineStr"/>
+      <c r="AG10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A11" s="9" t="n">
@@ -1951,41 +1931,37 @@
           <t>อัดจาระบีตามจุดที่อัดจาระบีทุกๆจุด</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="20" t="n"/>
-      <c r="P11" s="20" t="n"/>
-      <c r="Q11" s="20" t="n"/>
-      <c r="R11" s="20" t="n"/>
-      <c r="S11" s="20" t="n"/>
-      <c r="T11" s="20" t="n"/>
-      <c r="U11" s="20" t="n"/>
-      <c r="V11" s="20" t="n"/>
-      <c r="W11" s="20" t="n"/>
-      <c r="X11" s="20" t="n"/>
-      <c r="Y11" s="20" t="n"/>
-      <c r="Z11" s="20" t="n"/>
-      <c r="AA11" s="20" t="n"/>
-      <c r="AB11" s="20" t="n"/>
-      <c r="AC11" s="20" t="n"/>
-      <c r="AD11" s="20" t="n"/>
-      <c r="AE11" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF11" s="20" t="n"/>
-      <c r="AG11" s="20" t="n"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr"/>
+      <c r="M11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="inlineStr"/>
+      <c r="O11" s="20" t="inlineStr"/>
+      <c r="P11" s="20" t="inlineStr"/>
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="20" t="inlineStr"/>
+      <c r="V11" s="20" t="inlineStr"/>
+      <c r="W11" s="20" t="inlineStr"/>
+      <c r="X11" s="20" t="inlineStr"/>
+      <c r="Y11" s="20" t="inlineStr"/>
+      <c r="Z11" s="20" t="inlineStr"/>
+      <c r="AA11" s="20" t="inlineStr"/>
+      <c r="AB11" s="20" t="inlineStr"/>
+      <c r="AC11" s="20" t="inlineStr"/>
+      <c r="AD11" s="20" t="inlineStr"/>
+      <c r="AE11" s="20" t="inlineStr"/>
+      <c r="AF11" s="20" t="inlineStr"/>
+      <c r="AG11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A12" s="9" t="n">
@@ -1996,41 +1972,37 @@
           <t>ตรวจสอบใบมีด  บนและล่าง</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="20" t="n"/>
-      <c r="P12" s="20" t="n"/>
-      <c r="Q12" s="20" t="n"/>
-      <c r="R12" s="20" t="n"/>
-      <c r="S12" s="20" t="n"/>
-      <c r="T12" s="20" t="n"/>
-      <c r="U12" s="20" t="n"/>
-      <c r="V12" s="20" t="n"/>
-      <c r="W12" s="20" t="n"/>
-      <c r="X12" s="20" t="n"/>
-      <c r="Y12" s="20" t="n"/>
-      <c r="Z12" s="20" t="n"/>
-      <c r="AA12" s="20" t="n"/>
-      <c r="AB12" s="20" t="n"/>
-      <c r="AC12" s="20" t="n"/>
-      <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF12" s="20" t="n"/>
-      <c r="AG12" s="20" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="20" t="inlineStr"/>
+      <c r="W12" s="20" t="inlineStr"/>
+      <c r="X12" s="20" t="inlineStr"/>
+      <c r="Y12" s="20" t="inlineStr"/>
+      <c r="Z12" s="20" t="inlineStr"/>
+      <c r="AA12" s="20" t="inlineStr"/>
+      <c r="AB12" s="20" t="inlineStr"/>
+      <c r="AC12" s="20" t="inlineStr"/>
+      <c r="AD12" s="20" t="inlineStr"/>
+      <c r="AE12" s="20" t="inlineStr"/>
+      <c r="AF12" s="20" t="inlineStr"/>
+      <c r="AG12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A13" s="9" t="n">
@@ -2041,76 +2013,72 @@
           <t xml:space="preserve">ตรวจสอบความพร้อมสภาพโดยรวมของเครื่อง จักรและอุปกรณ์เสริมต่าง ๆ </t>
         </is>
       </c>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="n"/>
-      <c r="O13" s="20" t="n"/>
-      <c r="P13" s="20" t="n"/>
-      <c r="Q13" s="20" t="n"/>
-      <c r="R13" s="20" t="n"/>
-      <c r="S13" s="20" t="n"/>
-      <c r="T13" s="20" t="n"/>
-      <c r="U13" s="20" t="n"/>
-      <c r="V13" s="20" t="n"/>
-      <c r="W13" s="20" t="n"/>
-      <c r="X13" s="20" t="n"/>
-      <c r="Y13" s="20" t="n"/>
-      <c r="Z13" s="20" t="n"/>
-      <c r="AA13" s="20" t="n"/>
-      <c r="AB13" s="20" t="n"/>
-      <c r="AC13" s="20" t="n"/>
-      <c r="AD13" s="20" t="n"/>
-      <c r="AE13" s="39" t="inlineStr">
-        <is>
-          <t>พรมมา คาวไธสงค์</t>
-        </is>
-      </c>
-      <c r="AF13" s="20" t="n"/>
-      <c r="AG13" s="20" t="n"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="20" t="inlineStr"/>
+      <c r="W13" s="20" t="inlineStr"/>
+      <c r="X13" s="20" t="inlineStr"/>
+      <c r="Y13" s="20" t="inlineStr"/>
+      <c r="Z13" s="20" t="inlineStr"/>
+      <c r="AA13" s="20" t="inlineStr"/>
+      <c r="AB13" s="20" t="inlineStr"/>
+      <c r="AC13" s="20" t="inlineStr"/>
+      <c r="AD13" s="20" t="inlineStr"/>
+      <c r="AE13" s="39" t="inlineStr"/>
+      <c r="AF13" s="20" t="inlineStr"/>
+      <c r="AG13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="8" t="n"/>
       <c r="B14" s="7" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
-      <c r="G14" s="23" t="n"/>
-      <c r="H14" s="23" t="n"/>
-      <c r="I14" s="23" t="n"/>
-      <c r="J14" s="23" t="n"/>
-      <c r="K14" s="23" t="n"/>
-      <c r="L14" s="23" t="n"/>
-      <c r="M14" s="23" t="n"/>
-      <c r="N14" s="23" t="n"/>
-      <c r="O14" s="23" t="n"/>
-      <c r="P14" s="23" t="n"/>
-      <c r="Q14" s="23" t="n"/>
-      <c r="R14" s="23" t="n"/>
-      <c r="S14" s="23" t="n"/>
-      <c r="T14" s="23" t="n"/>
-      <c r="U14" s="23" t="n"/>
-      <c r="V14" s="23" t="n"/>
-      <c r="W14" s="23" t="n"/>
-      <c r="X14" s="23" t="n"/>
-      <c r="Y14" s="23" t="n"/>
-      <c r="Z14" s="23" t="n"/>
-      <c r="AA14" s="37" t="n"/>
-      <c r="AB14" s="23" t="n"/>
-      <c r="AC14" s="23" t="n"/>
-      <c r="AD14" s="23" t="n"/>
-      <c r="AE14" s="23" t="n"/>
-      <c r="AF14" s="23" t="n"/>
-      <c r="AG14" s="23" t="n"/>
+      <c r="C14" s="23" t="inlineStr"/>
+      <c r="D14" s="23" t="inlineStr"/>
+      <c r="E14" s="23" t="inlineStr"/>
+      <c r="F14" s="23" t="inlineStr"/>
+      <c r="G14" s="23" t="inlineStr"/>
+      <c r="H14" s="23" t="inlineStr"/>
+      <c r="I14" s="23" t="inlineStr"/>
+      <c r="J14" s="23" t="inlineStr"/>
+      <c r="K14" s="23" t="inlineStr"/>
+      <c r="L14" s="23" t="inlineStr"/>
+      <c r="M14" s="23" t="inlineStr"/>
+      <c r="N14" s="23" t="inlineStr"/>
+      <c r="O14" s="23" t="inlineStr"/>
+      <c r="P14" s="23" t="inlineStr"/>
+      <c r="Q14" s="23" t="inlineStr"/>
+      <c r="R14" s="23" t="inlineStr"/>
+      <c r="S14" s="23" t="inlineStr"/>
+      <c r="T14" s="23" t="inlineStr"/>
+      <c r="U14" s="23" t="inlineStr"/>
+      <c r="V14" s="23" t="inlineStr"/>
+      <c r="W14" s="23" t="inlineStr"/>
+      <c r="X14" s="23" t="inlineStr"/>
+      <c r="Y14" s="23" t="inlineStr"/>
+      <c r="Z14" s="23" t="inlineStr"/>
+      <c r="AA14" s="37" t="inlineStr"/>
+      <c r="AB14" s="23" t="inlineStr"/>
+      <c r="AC14" s="23" t="inlineStr"/>
+      <c r="AD14" s="23" t="inlineStr"/>
+      <c r="AE14" s="23" t="inlineStr"/>
+      <c r="AF14" s="23" t="inlineStr"/>
+      <c r="AG14" s="23" t="inlineStr"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="B15" s="6" t="n"/>
@@ -2214,7 +2182,9 @@
       <c r="AF17" s="24" t="n"/>
       <c r="AG17" s="24" t="n"/>
     </row>
-    <row r="18" ht="12" customHeight="1"/>
+    <row r="18" ht="12" customHeight="1">
+      <c r="B18" t="inlineStr"/>
+    </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="B19" s="17" t="inlineStr">
         <is>

--- a/FM-MN-07_CUTTING-01.xlsx
+++ b/FM-MN-07_CUTTING-01.xlsx
@@ -1731,7 +1731,11 @@
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
       <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I6" s="20" t="inlineStr"/>
       <c r="J6" s="20" t="inlineStr"/>
       <c r="K6" s="20" t="inlineStr"/>
@@ -1772,7 +1776,11 @@
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
       <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
       <c r="K7" s="20" t="inlineStr"/>
@@ -1813,7 +1821,11 @@
       <c r="E8" s="20" t="inlineStr"/>
       <c r="F8" s="20" t="inlineStr"/>
       <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="20" t="inlineStr"/>
       <c r="J8" s="20" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr"/>
@@ -1854,7 +1866,11 @@
       <c r="E9" s="20" t="inlineStr"/>
       <c r="F9" s="20" t="inlineStr"/>
       <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="20" t="inlineStr"/>
       <c r="J9" s="20" t="inlineStr"/>
       <c r="K9" s="20" t="inlineStr"/>
@@ -1895,7 +1911,11 @@
       <c r="E10" s="20" t="inlineStr"/>
       <c r="F10" s="20" t="inlineStr"/>
       <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
       <c r="K10" s="20" t="inlineStr"/>
@@ -1936,7 +1956,11 @@
       <c r="E11" s="20" t="inlineStr"/>
       <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="20" t="inlineStr"/>
       <c r="J11" s="20" t="inlineStr"/>
       <c r="K11" s="20" t="inlineStr"/>
@@ -1977,7 +2001,11 @@
       <c r="E12" s="20" t="inlineStr"/>
       <c r="F12" s="20" t="inlineStr"/>
       <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="20" t="inlineStr"/>
       <c r="J12" s="20" t="inlineStr"/>
       <c r="K12" s="20" t="inlineStr"/>
@@ -2018,7 +2046,11 @@
       <c r="E13" s="20" t="inlineStr"/>
       <c r="F13" s="20" t="inlineStr"/>
       <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
+      <c r="H13" s="39" t="inlineStr">
+        <is>
+          <t>วชิรทย์</t>
+        </is>
+      </c>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
       <c r="K13" s="20" t="inlineStr"/>
@@ -2182,9 +2214,7 @@
       <c r="AF17" s="24" t="n"/>
       <c r="AG17" s="24" t="n"/>
     </row>
-    <row r="18" ht="12" customHeight="1">
-      <c r="B18" t="inlineStr"/>
-    </row>
+    <row r="18" ht="12" customHeight="1"/>
     <row r="19" ht="19.5" customHeight="1">
       <c r="B19" s="17" t="inlineStr">
         <is>

--- a/FM-MN-07_CUTTING-01.xlsx
+++ b/FM-MN-07_CUTTING-01.xlsx
@@ -1736,7 +1736,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J6" s="20" t="inlineStr"/>
       <c r="K6" s="20" t="inlineStr"/>
       <c r="L6" s="20" t="inlineStr"/>
@@ -1781,7 +1785,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="20" t="inlineStr"/>
       <c r="K7" s="20" t="inlineStr"/>
       <c r="L7" s="20" t="inlineStr"/>
@@ -1826,7 +1834,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="20" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr"/>
       <c r="L8" s="20" t="inlineStr"/>
@@ -1871,7 +1883,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="20" t="inlineStr"/>
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
@@ -1916,7 +1932,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="20" t="inlineStr"/>
       <c r="K10" s="20" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr"/>
@@ -1961,7 +1981,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="20" t="inlineStr"/>
       <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr"/>
@@ -2006,7 +2030,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="20" t="inlineStr"/>
       <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
@@ -2051,7 +2079,11 @@
           <t>วชิรทย์</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
+      <c r="I13" s="39" t="inlineStr">
+        <is>
+          <t>วชิรวิทย์</t>
+        </is>
+      </c>
       <c r="J13" s="20" t="inlineStr"/>
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="inlineStr"/>

--- a/FM-MN-07_CUTTING-01.xlsx
+++ b/FM-MN-07_CUTTING-01.xlsx
@@ -1741,7 +1741,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K6" s="20" t="inlineStr"/>
       <c r="L6" s="20" t="inlineStr"/>
       <c r="M6" s="20" t="inlineStr"/>
@@ -1790,7 +1794,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K7" s="20" t="inlineStr"/>
       <c r="L7" s="20" t="inlineStr"/>
       <c r="M7" s="20" t="inlineStr"/>
@@ -1839,7 +1847,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="20" t="inlineStr"/>
       <c r="L8" s="20" t="inlineStr"/>
       <c r="M8" s="20" t="inlineStr"/>
@@ -1888,7 +1900,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
       <c r="M9" s="20" t="inlineStr"/>
@@ -1937,7 +1953,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="20" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr"/>
       <c r="M10" s="20" t="inlineStr"/>
@@ -1986,7 +2006,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr"/>
       <c r="M11" s="20" t="inlineStr"/>
@@ -2035,7 +2059,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
       <c r="M12" s="20" t="inlineStr"/>
@@ -2084,7 +2112,11 @@
           <t>วชิรวิทย์</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="J13" s="39" t="inlineStr">
+        <is>
+          <t>วชิรวิทย์</t>
+        </is>
+      </c>
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="inlineStr"/>
       <c r="M13" s="20" t="inlineStr"/>

--- a/FM-MN-07_CUTTING-01.xlsx
+++ b/FM-MN-07_CUTTING-01.xlsx
@@ -1747,7 +1747,11 @@
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M6" s="20" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr"/>
       <c r="O6" s="20" t="inlineStr"/>
@@ -1800,7 +1804,11 @@
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M7" s="20" t="inlineStr"/>
       <c r="N7" s="20" t="inlineStr"/>
       <c r="O7" s="20" t="inlineStr"/>
@@ -1853,7 +1861,11 @@
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="20" t="inlineStr"/>
       <c r="N8" s="20" t="inlineStr"/>
       <c r="O8" s="20" t="inlineStr"/>
@@ -1906,7 +1918,11 @@
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="20" t="inlineStr"/>
       <c r="N9" s="20" t="inlineStr"/>
       <c r="O9" s="20" t="inlineStr"/>
@@ -1959,7 +1975,11 @@
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="20" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr"/>
       <c r="O10" s="20" t="inlineStr"/>
@@ -2012,7 +2032,11 @@
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="20" t="inlineStr"/>
       <c r="N11" s="20" t="inlineStr"/>
       <c r="O11" s="20" t="inlineStr"/>
@@ -2065,7 +2089,11 @@
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="20" t="inlineStr"/>
       <c r="N12" s="20" t="inlineStr"/>
       <c r="O12" s="20" t="inlineStr"/>
@@ -2118,7 +2146,11 @@
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
+      <c r="L13" s="39" t="inlineStr">
+        <is>
+          <t>วชิรวิทย์</t>
+        </is>
+      </c>
       <c r="M13" s="20" t="inlineStr"/>
       <c r="N13" s="20" t="inlineStr"/>
       <c r="O13" s="20" t="inlineStr"/>
